--- a/assets/schedule.xlsx
+++ b/assets/schedule.xlsx
@@ -40,7 +40,7 @@
     <t>Dan Sid Solo</t>
   </si>
   <si>
-    <t>Indie RockAcoustic Pop-Classics Crossover</t>
+    <t>Acoustic Pop-Classics Crossover</t>
   </si>
   <si>
     <t>@danielsiddy</t>
